--- a/artfynd/A 6025-2024 artfynd.xlsx
+++ b/artfynd/A 6025-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>114862498</v>
       </c>
       <c r="B2" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,7 +707,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rosendal (Rosendal), Sm</t>
+          <t>Rosendal, Rosendal, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
